--- a/histograms/histogram_frac_p_valence_electrons.xlsx
+++ b/histograms/histogram_frac_p_valence_electrons.xlsx
@@ -445,7 +445,7 @@
         <v>0.251375</v>
       </c>
       <c r="B2" t="n">
-        <v>223</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -461,7 +461,7 @@
         <v>0.276875</v>
       </c>
       <c r="B4" t="n">
-        <v>478</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -469,7 +469,7 @@
         <v>0.289625</v>
       </c>
       <c r="B5" t="n">
-        <v>703</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -477,7 +477,7 @@
         <v>0.3023749999999999</v>
       </c>
       <c r="B6" t="n">
-        <v>898</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         <v>0.315125</v>
       </c>
       <c r="B7" t="n">
-        <v>227</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -493,7 +493,7 @@
         <v>0.327875</v>
       </c>
       <c r="B8" t="n">
-        <v>1097</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
@@ -501,7 +501,7 @@
         <v>0.340625</v>
       </c>
       <c r="B9" t="n">
-        <v>124</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -509,7 +509,7 @@
         <v>0.353375</v>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -517,7 +517,7 @@
         <v>0.366125</v>
       </c>
       <c r="B11" t="n">
-        <v>203</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -525,7 +525,7 @@
         <v>0.378875</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -533,7 +533,7 @@
         <v>0.391625</v>
       </c>
       <c r="B13" t="n">
-        <v>312</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0.404375</v>
       </c>
       <c r="B14" t="n">
-        <v>1286</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15">
@@ -549,7 +549,7 @@
         <v>0.417125</v>
       </c>
       <c r="B15" t="n">
-        <v>1845</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -557,7 +557,7 @@
         <v>0.429875</v>
       </c>
       <c r="B16" t="n">
-        <v>1866</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0.442625</v>
       </c>
       <c r="B17" t="n">
-        <v>818</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0.455375</v>
       </c>
       <c r="B18" t="n">
-        <v>666</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0.468125</v>
       </c>
       <c r="B19" t="n">
-        <v>675</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -589,7 +589,7 @@
         <v>0.4808750000000001</v>
       </c>
       <c r="B20" t="n">
-        <v>1757</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21">
@@ -597,7 +597,7 @@
         <v>0.493625</v>
       </c>
       <c r="B21" t="n">
-        <v>13100</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
